--- a/ValueSet-DocumentLOINCCodelist.xlsx
+++ b/ValueSet-DocumentLOINCCodelist.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="42">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-03T16:43:05+00:00</t>
+    <t>2024-10-03T16:45:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -85,6 +85,9 @@
   </si>
   <si>
     <t>Description</t>
+  </si>
+  <si>
+    <t>Docuemnt Class en Type LOINC codes die we vinden zonder display, zodat we wel een display in Nederlands kunnen tonen</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -376,28 +379,30 @@
       <c r="A13" t="s" s="2">
         <v>23</v>
       </c>
-      <c r="B13" s="2"/>
+      <c r="B13" t="s" s="2">
+        <v>24</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -416,7 +421,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B1" t="s" s="1">
         <v>23</v>
@@ -424,50 +429,50 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>

--- a/ValueSet-DocumentLOINCCodelist.xlsx
+++ b/ValueSet-DocumentLOINCCodelist.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-03T16:45:10+00:00</t>
+    <t>2024-10-08T12:11:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-DocumentLOINCCodelist.xlsx
+++ b/ValueSet-DocumentLOINCCodelist.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-08T12:11:06+00:00</t>
+    <t>2024-10-08T14:52:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-DocumentLOINCCodelist.xlsx
+++ b/ValueSet-DocumentLOINCCodelist.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-08T14:52:43+00:00</t>
+    <t>2024-10-08T15:01:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-DocumentLOINCCodelist.xlsx
+++ b/ValueSet-DocumentLOINCCodelist.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-08T15:01:02+00:00</t>
+    <t>2024-10-08T15:17:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-DocumentLOINCCodelist.xlsx
+++ b/ValueSet-DocumentLOINCCodelist.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-08T15:17:59+00:00</t>
+    <t>2024-10-14T07:51:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-DocumentLOINCCodelist.xlsx
+++ b/ValueSet-DocumentLOINCCodelist.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-14T07:51:32+00:00</t>
+    <t>2024-10-15T11:57:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-DocumentLOINCCodelist.xlsx
+++ b/ValueSet-DocumentLOINCCodelist.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-15T11:57:40+00:00</t>
+    <t>2024-10-15T13:32:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-DocumentLOINCCodelist.xlsx
+++ b/ValueSet-DocumentLOINCCodelist.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-15T13:32:14+00:00</t>
+    <t>2024-10-17T08:27:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-DocumentLOINCCodelist.xlsx
+++ b/ValueSet-DocumentLOINCCodelist.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.6.0</t>
+    <t>1.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-17T08:27:04+00:00</t>
+    <t>2024-10-17T08:35:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-DocumentLOINCCodelist.xlsx
+++ b/ValueSet-DocumentLOINCCodelist.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-17T08:35:21+00:00</t>
+    <t>2024-10-26T09:12:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-DocumentLOINCCodelist.xlsx
+++ b/ValueSet-DocumentLOINCCodelist.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-26T09:12:53+00:00</t>
+    <t>2024-10-29T13:54:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-DocumentLOINCCodelist.xlsx
+++ b/ValueSet-DocumentLOINCCodelist.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-29T13:54:17+00:00</t>
+    <t>2024-10-30T11:37:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-DocumentLOINCCodelist.xlsx
+++ b/ValueSet-DocumentLOINCCodelist.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-30T11:37:59+00:00</t>
+    <t>2024-11-04T07:59:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-DocumentLOINCCodelist.xlsx
+++ b/ValueSet-DocumentLOINCCodelist.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-04T07:59:20+00:00</t>
+    <t>2024-11-06T14:12:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-DocumentLOINCCodelist.xlsx
+++ b/ValueSet-DocumentLOINCCodelist.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-06T14:12:43+00:00</t>
+    <t>2024-11-06T21:19:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-DocumentLOINCCodelist.xlsx
+++ b/ValueSet-DocumentLOINCCodelist.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-06T21:19:30+00:00</t>
+    <t>2024-11-12T08:18:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-DocumentLOINCCodelist.xlsx
+++ b/ValueSet-DocumentLOINCCodelist.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.7.0</t>
+    <t>1.8.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T08:18:00+00:00</t>
+    <t>2024-11-12T08:24:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-DocumentLOINCCodelist.xlsx
+++ b/ValueSet-DocumentLOINCCodelist.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T08:24:06+00:00</t>
+    <t>2024-11-12T10:55:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-DocumentLOINCCodelist.xlsx
+++ b/ValueSet-DocumentLOINCCodelist.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T10:55:49+00:00</t>
+    <t>2024-11-12T11:26:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-DocumentLOINCCodelist.xlsx
+++ b/ValueSet-DocumentLOINCCodelist.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T11:26:12+00:00</t>
+    <t>2024-11-12T16:51:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-DocumentLOINCCodelist.xlsx
+++ b/ValueSet-DocumentLOINCCodelist.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T16:51:17+00:00</t>
+    <t>2024-11-19T12:47:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-DocumentLOINCCodelist.xlsx
+++ b/ValueSet-DocumentLOINCCodelist.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-19T12:47:37+00:00</t>
+    <t>2024-11-19T15:01:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-DocumentLOINCCodelist.xlsx
+++ b/ValueSet-DocumentLOINCCodelist.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-19T15:01:01+00:00</t>
+    <t>2024-11-24T09:20:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-DocumentLOINCCodelist.xlsx
+++ b/ValueSet-DocumentLOINCCodelist.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-24T09:20:45+00:00</t>
+    <t>2024-11-25T09:16:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-DocumentLOINCCodelist.xlsx
+++ b/ValueSet-DocumentLOINCCodelist.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-25T09:16:03+00:00</t>
+    <t>2024-11-25T09:33:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-DocumentLOINCCodelist.xlsx
+++ b/ValueSet-DocumentLOINCCodelist.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-25T09:33:17+00:00</t>
+    <t>2024-11-25T09:37:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-DocumentLOINCCodelist.xlsx
+++ b/ValueSet-DocumentLOINCCodelist.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.8.0</t>
+    <t>1.9.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-25T09:37:54+00:00</t>
+    <t>2024-11-25T09:42:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-DocumentLOINCCodelist.xlsx
+++ b/ValueSet-DocumentLOINCCodelist.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-25T09:42:11+00:00</t>
+    <t>2024-11-25T11:02:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-DocumentLOINCCodelist.xlsx
+++ b/ValueSet-DocumentLOINCCodelist.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-25T11:02:10+00:00</t>
+    <t>2024-11-28T08:25:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-DocumentLOINCCodelist.xlsx
+++ b/ValueSet-DocumentLOINCCodelist.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-28T08:25:00+00:00</t>
+    <t>2024-11-28T17:50:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-DocumentLOINCCodelist.xlsx
+++ b/ValueSet-DocumentLOINCCodelist.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-28T17:50:24+00:00</t>
+    <t>2024-11-30T09:54:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-DocumentLOINCCodelist.xlsx
+++ b/ValueSet-DocumentLOINCCodelist.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-30T09:54:10+00:00</t>
+    <t>2024-12-03T09:13:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-DocumentLOINCCodelist.xlsx
+++ b/ValueSet-DocumentLOINCCodelist.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-03T09:13:19+00:00</t>
+    <t>2024-12-03T10:04:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-DocumentLOINCCodelist.xlsx
+++ b/ValueSet-DocumentLOINCCodelist.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-03T10:04:50+00:00</t>
+    <t>2024-12-05T14:20:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-DocumentLOINCCodelist.xlsx
+++ b/ValueSet-DocumentLOINCCodelist.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-05T14:20:46+00:00</t>
+    <t>2024-12-10T07:51:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-DocumentLOINCCodelist.xlsx
+++ b/ValueSet-DocumentLOINCCodelist.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-10T07:51:08+00:00</t>
+    <t>2024-12-10T08:19:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-DocumentLOINCCodelist.xlsx
+++ b/ValueSet-DocumentLOINCCodelist.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.9.0</t>
+    <t>1.10.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-10T08:19:29+00:00</t>
+    <t>2024-12-10T08:34:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-DocumentLOINCCodelist.xlsx
+++ b/ValueSet-DocumentLOINCCodelist.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-10T08:34:20+00:00</t>
+    <t>2024-12-10T08:45:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-DocumentLOINCCodelist.xlsx
+++ b/ValueSet-DocumentLOINCCodelist.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-10T08:45:26+00:00</t>
+    <t>2024-12-18T07:23:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-DocumentLOINCCodelist.xlsx
+++ b/ValueSet-DocumentLOINCCodelist.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://hl7.nl/fhir/zorgviewer/ValueSet/DocumentLOINCCodelist</t>
+    <t>http://fhir.hl7.nl/zorgviewer/ValueSet/DocumentLOINCCodelist</t>
   </si>
   <si>
     <t>Version</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-18T07:23:17+00:00</t>
+    <t>2024-12-23T09:34:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-DocumentLOINCCodelist.xlsx
+++ b/ValueSet-DocumentLOINCCodelist.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-23T09:34:32+00:00</t>
+    <t>2024-12-23T15:35:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-DocumentLOINCCodelist.xlsx
+++ b/ValueSet-DocumentLOINCCodelist.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-23T15:35:28+00:00</t>
+    <t>2024-12-27T09:44:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-DocumentLOINCCodelist.xlsx
+++ b/ValueSet-DocumentLOINCCodelist.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-27T09:44:10+00:00</t>
+    <t>2024-12-27T09:59:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-DocumentLOINCCodelist.xlsx
+++ b/ValueSet-DocumentLOINCCodelist.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.10.0</t>
+    <t>1.11.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-27T09:59:08+00:00</t>
+    <t>2025-01-02T11:11:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-DocumentLOINCCodelist.xlsx
+++ b/ValueSet-DocumentLOINCCodelist.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-02T11:11:09+00:00</t>
+    <t>2025-01-02T12:37:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-DocumentLOINCCodelist.xlsx
+++ b/ValueSet-DocumentLOINCCodelist.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-02T12:37:15+00:00</t>
+    <t>2025-01-05T10:27:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -96,7 +96,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>This value set includes content from LOINC</t>
+    <t>This material contains content from LOINC (http://loinc.org). LOINC is copyright © 1995-2020, Regenstrief Institute, Inc. and the Logical Observation Identifiers Names and Codes (LOINC) Committee and is available at no cost under the license at http://loinc.org/license. LOINC® is a registered United States trademark of Regenstrief Institute, Inc</t>
   </si>
   <si>
     <t>Immutable</t>

--- a/ValueSet-DocumentLOINCCodelist.xlsx
+++ b/ValueSet-DocumentLOINCCodelist.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-05T10:27:23+00:00</t>
+    <t>2025-01-05T10:53:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-DocumentLOINCCodelist.xlsx
+++ b/ValueSet-DocumentLOINCCodelist.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-05T10:53:29+00:00</t>
+    <t>2025-01-06T15:42:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-DocumentLOINCCodelist.xlsx
+++ b/ValueSet-DocumentLOINCCodelist.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-06T15:42:07+00:00</t>
+    <t>2025-01-06T15:50:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-DocumentLOINCCodelist.xlsx
+++ b/ValueSet-DocumentLOINCCodelist.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-06T15:50:28+00:00</t>
+    <t>2025-01-06T16:52:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-DocumentLOINCCodelist.xlsx
+++ b/ValueSet-DocumentLOINCCodelist.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-06T16:52:49+00:00</t>
+    <t>2025-01-06T17:00:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-DocumentLOINCCodelist.xlsx
+++ b/ValueSet-DocumentLOINCCodelist.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-06T17:00:55+00:00</t>
+    <t>2025-01-20T15:02:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-DocumentLOINCCodelist.xlsx
+++ b/ValueSet-DocumentLOINCCodelist.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-20T15:02:53+00:00</t>
+    <t>2025-01-28T20:06:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-DocumentLOINCCodelist.xlsx
+++ b/ValueSet-DocumentLOINCCodelist.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.11.0</t>
+    <t>1.12.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-28T20:06:40+00:00</t>
+    <t>2025-01-28T20:08:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-DocumentLOINCCodelist.xlsx
+++ b/ValueSet-DocumentLOINCCodelist.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-28T20:08:20+00:00</t>
+    <t>2025-01-28T20:50:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-DocumentLOINCCodelist.xlsx
+++ b/ValueSet-DocumentLOINCCodelist.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-28T20:50:34+00:00</t>
+    <t>2025-01-31T07:22:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-DocumentLOINCCodelist.xlsx
+++ b/ValueSet-DocumentLOINCCodelist.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-31T07:22:48+00:00</t>
+    <t>2025-01-31T13:40:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-DocumentLOINCCodelist.xlsx
+++ b/ValueSet-DocumentLOINCCodelist.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-31T13:40:12+00:00</t>
+    <t>2025-02-03T11:19:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-DocumentLOINCCodelist.xlsx
+++ b/ValueSet-DocumentLOINCCodelist.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-03T11:19:03+00:00</t>
+    <t>2025-02-03T16:53:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-DocumentLOINCCodelist.xlsx
+++ b/ValueSet-DocumentLOINCCodelist.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-03T16:53:34+00:00</t>
+    <t>2025-02-04T12:12:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-DocumentLOINCCodelist.xlsx
+++ b/ValueSet-DocumentLOINCCodelist.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-04T12:12:36+00:00</t>
+    <t>2025-02-05T13:44:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-DocumentLOINCCodelist.xlsx
+++ b/ValueSet-DocumentLOINCCodelist.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T13:44:35+00:00</t>
+    <t>2025-02-05T14:01:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-DocumentLOINCCodelist.xlsx
+++ b/ValueSet-DocumentLOINCCodelist.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T14:01:06+00:00</t>
+    <t>2025-02-05T14:12:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-DocumentLOINCCodelist.xlsx
+++ b/ValueSet-DocumentLOINCCodelist.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T14:12:35+00:00</t>
+    <t>2025-02-12T15:28:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-DocumentLOINCCodelist.xlsx
+++ b/ValueSet-DocumentLOINCCodelist.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-12T15:28:44+00:00</t>
+    <t>2025-02-13T13:25:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-DocumentLOINCCodelist.xlsx
+++ b/ValueSet-DocumentLOINCCodelist.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T13:25:12+00:00</t>
+    <t>2025-02-13T13:30:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-DocumentLOINCCodelist.xlsx
+++ b/ValueSet-DocumentLOINCCodelist.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T13:30:29+00:00</t>
+    <t>2025-02-18T14:04:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-DocumentLOINCCodelist.xlsx
+++ b/ValueSet-DocumentLOINCCodelist.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T14:04:23+00:00</t>
+    <t>2025-02-24T11:20:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-DocumentLOINCCodelist.xlsx
+++ b/ValueSet-DocumentLOINCCodelist.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T11:20:06+00:00</t>
+    <t>2025-02-24T11:23:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-DocumentLOINCCodelist.xlsx
+++ b/ValueSet-DocumentLOINCCodelist.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T11:23:09+00:00</t>
+    <t>2025-02-24T11:25:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-DocumentLOINCCodelist.xlsx
+++ b/ValueSet-DocumentLOINCCodelist.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T11:25:44+00:00</t>
+    <t>2025-02-24T11:27:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-DocumentLOINCCodelist.xlsx
+++ b/ValueSet-DocumentLOINCCodelist.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T11:27:07+00:00</t>
+    <t>2025-02-24T13:31:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-DocumentLOINCCodelist.xlsx
+++ b/ValueSet-DocumentLOINCCodelist.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T13:31:19+00:00</t>
+    <t>2025-02-24T15:55:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-DocumentLOINCCodelist.xlsx
+++ b/ValueSet-DocumentLOINCCodelist.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T15:55:23+00:00</t>
+    <t>2025-02-24T16:22:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-DocumentLOINCCodelist.xlsx
+++ b/ValueSet-DocumentLOINCCodelist.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T16:22:43+00:00</t>
+    <t>2025-02-25T09:38:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-DocumentLOINCCodelist.xlsx
+++ b/ValueSet-DocumentLOINCCodelist.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-25T09:38:10+00:00</t>
+    <t>2025-02-25T09:39:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-DocumentLOINCCodelist.xlsx
+++ b/ValueSet-DocumentLOINCCodelist.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-25T09:39:04+00:00</t>
+    <t>2025-02-25T20:48:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-DocumentLOINCCodelist.xlsx
+++ b/ValueSet-DocumentLOINCCodelist.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-25T20:48:56+00:00</t>
+    <t>2025-02-25T21:05:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-DocumentLOINCCodelist.xlsx
+++ b/ValueSet-DocumentLOINCCodelist.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-25T21:05:22+00:00</t>
+    <t>2025-02-26T07:46:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-DocumentLOINCCodelist.xlsx
+++ b/ValueSet-DocumentLOINCCodelist.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-26T07:46:44+00:00</t>
+    <t>2025-02-26T13:03:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-DocumentLOINCCodelist.xlsx
+++ b/ValueSet-DocumentLOINCCodelist.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-26T13:03:44+00:00</t>
+    <t>2025-02-26T13:09:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-DocumentLOINCCodelist.xlsx
+++ b/ValueSet-DocumentLOINCCodelist.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-26T13:09:25+00:00</t>
+    <t>2025-02-26T14:34:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-DocumentLOINCCodelist.xlsx
+++ b/ValueSet-DocumentLOINCCodelist.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-26T14:34:33+00:00</t>
+    <t>2025-02-26T14:37:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-DocumentLOINCCodelist.xlsx
+++ b/ValueSet-DocumentLOINCCodelist.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-26T14:37:20+00:00</t>
+    <t>2025-02-28T09:54:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-DocumentLOINCCodelist.xlsx
+++ b/ValueSet-DocumentLOINCCodelist.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-28T09:54:46+00:00</t>
+    <t>2025-02-28T10:33:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-DocumentLOINCCodelist.xlsx
+++ b/ValueSet-DocumentLOINCCodelist.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-28T10:33:33+00:00</t>
+    <t>2025-02-28T10:57:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-DocumentLOINCCodelist.xlsx
+++ b/ValueSet-DocumentLOINCCodelist.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-28T10:57:51+00:00</t>
+    <t>2025-02-28T11:01:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-DocumentLOINCCodelist.xlsx
+++ b/ValueSet-DocumentLOINCCodelist.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-28T11:01:07+00:00</t>
+    <t>2025-02-28T11:11:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-DocumentLOINCCodelist.xlsx
+++ b/ValueSet-DocumentLOINCCodelist.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-28T11:11:13+00:00</t>
+    <t>2025-02-28T11:13:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-DocumentLOINCCodelist.xlsx
+++ b/ValueSet-DocumentLOINCCodelist.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-28T11:13:38+00:00</t>
+    <t>2025-02-28T11:38:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-DocumentLOINCCodelist.xlsx
+++ b/ValueSet-DocumentLOINCCodelist.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-28T11:38:05+00:00</t>
+    <t>2025-02-28T11:39:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-DocumentLOINCCodelist.xlsx
+++ b/ValueSet-DocumentLOINCCodelist.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-28T11:39:24+00:00</t>
+    <t>2025-02-28T11:59:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-DocumentLOINCCodelist.xlsx
+++ b/ValueSet-DocumentLOINCCodelist.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-28T11:59:16+00:00</t>
+    <t>2025-03-03T08:47:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-DocumentLOINCCodelist.xlsx
+++ b/ValueSet-DocumentLOINCCodelist.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-03T08:47:24+00:00</t>
+    <t>2025-03-04T09:51:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-DocumentLOINCCodelist.xlsx
+++ b/ValueSet-DocumentLOINCCodelist.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-04T09:51:39+00:00</t>
+    <t>2025-03-04T10:31:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-DocumentLOINCCodelist.xlsx
+++ b/ValueSet-DocumentLOINCCodelist.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-04T10:31:42+00:00</t>
+    <t>2025-03-05T06:48:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-DocumentLOINCCodelist.xlsx
+++ b/ValueSet-DocumentLOINCCodelist.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-05T06:48:27+00:00</t>
+    <t>2025-03-05T13:19:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-DocumentLOINCCodelist.xlsx
+++ b/ValueSet-DocumentLOINCCodelist.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-05T13:19:54+00:00</t>
+    <t>2025-03-05T13:45:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-DocumentLOINCCodelist.xlsx
+++ b/ValueSet-DocumentLOINCCodelist.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-05T13:45:25+00:00</t>
+    <t>2025-03-05T16:01:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-DocumentLOINCCodelist.xlsx
+++ b/ValueSet-DocumentLOINCCodelist.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-05T16:01:47+00:00</t>
+    <t>2025-03-06T16:40:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-DocumentLOINCCodelist.xlsx
+++ b/ValueSet-DocumentLOINCCodelist.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-06T16:40:55+00:00</t>
+    <t>2025-03-09T10:18:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-DocumentLOINCCodelist.xlsx
+++ b/ValueSet-DocumentLOINCCodelist.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-09T10:18:56+00:00</t>
+    <t>2025-03-09T10:31:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-DocumentLOINCCodelist.xlsx
+++ b/ValueSet-DocumentLOINCCodelist.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-09T10:31:47+00:00</t>
+    <t>2025-03-10T07:49:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-DocumentLOINCCodelist.xlsx
+++ b/ValueSet-DocumentLOINCCodelist.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-10T07:49:31+00:00</t>
+    <t>2025-03-10T07:56:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-DocumentLOINCCodelist.xlsx
+++ b/ValueSet-DocumentLOINCCodelist.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-10T07:56:47+00:00</t>
+    <t>2025-03-12T11:31:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-DocumentLOINCCodelist.xlsx
+++ b/ValueSet-DocumentLOINCCodelist.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-12T11:31:39+00:00</t>
+    <t>2025-03-12T11:55:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-DocumentLOINCCodelist.xlsx
+++ b/ValueSet-DocumentLOINCCodelist.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-12T11:55:43+00:00</t>
+    <t>2025-03-12T11:57:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-DocumentLOINCCodelist.xlsx
+++ b/ValueSet-DocumentLOINCCodelist.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-12T11:57:23+00:00</t>
+    <t>2025-03-13T10:18:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-DocumentLOINCCodelist.xlsx
+++ b/ValueSet-DocumentLOINCCodelist.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-13T10:18:09+00:00</t>
+    <t>2025-03-18T08:10:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-DocumentLOINCCodelist.xlsx
+++ b/ValueSet-DocumentLOINCCodelist.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-18T08:10:21+00:00</t>
+    <t>2025-03-18T10:21:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-DocumentLOINCCodelist.xlsx
+++ b/ValueSet-DocumentLOINCCodelist.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.12.0</t>
+    <t>1.13.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-18T10:21:48+00:00</t>
+    <t>2025-03-18T10:31:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-DocumentLOINCCodelist.xlsx
+++ b/ValueSet-DocumentLOINCCodelist.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-18T10:31:44+00:00</t>
+    <t>2025-03-18T13:21:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-DocumentLOINCCodelist.xlsx
+++ b/ValueSet-DocumentLOINCCodelist.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-18T13:21:59+00:00</t>
+    <t>2025-03-18T14:10:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-DocumentLOINCCodelist.xlsx
+++ b/ValueSet-DocumentLOINCCodelist.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-18T14:10:18+00:00</t>
+    <t>2025-03-24T10:28:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-DocumentLOINCCodelist.xlsx
+++ b/ValueSet-DocumentLOINCCodelist.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-24T10:28:29+00:00</t>
+    <t>2025-03-24T10:49:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-DocumentLOINCCodelist.xlsx
+++ b/ValueSet-DocumentLOINCCodelist.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-24T10:49:00+00:00</t>
+    <t>2025-03-24T11:21:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-DocumentLOINCCodelist.xlsx
+++ b/ValueSet-DocumentLOINCCodelist.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-24T11:21:14+00:00</t>
+    <t>2025-03-24T11:37:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-DocumentLOINCCodelist.xlsx
+++ b/ValueSet-DocumentLOINCCodelist.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-24T11:37:37+00:00</t>
+    <t>2025-04-01T10:33:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-DocumentLOINCCodelist.xlsx
+++ b/ValueSet-DocumentLOINCCodelist.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-01T10:33:26+00:00</t>
+    <t>2025-04-01T10:36:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-DocumentLOINCCodelist.xlsx
+++ b/ValueSet-DocumentLOINCCodelist.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.13.0</t>
+    <t>1.14.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-01T10:36:45+00:00</t>
+    <t>2025-04-01T10:40:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-DocumentLOINCCodelist.xlsx
+++ b/ValueSet-DocumentLOINCCodelist.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-01T10:40:06+00:00</t>
+    <t>2025-04-01T11:02:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-DocumentLOINCCodelist.xlsx
+++ b/ValueSet-DocumentLOINCCodelist.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-01T11:02:34+00:00</t>
+    <t>2025-04-07T09:57:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-DocumentLOINCCodelist.xlsx
+++ b/ValueSet-DocumentLOINCCodelist.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-07T09:57:36+00:00</t>
+    <t>2025-04-07T10:44:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-DocumentLOINCCodelist.xlsx
+++ b/ValueSet-DocumentLOINCCodelist.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-07T10:44:48+00:00</t>
+    <t>2025-04-07T14:17:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-DocumentLOINCCodelist.xlsx
+++ b/ValueSet-DocumentLOINCCodelist.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-07T14:17:30+00:00</t>
+    <t>2025-04-09T20:29:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-DocumentLOINCCodelist.xlsx
+++ b/ValueSet-DocumentLOINCCodelist.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-09T20:29:26+00:00</t>
+    <t>2025-04-09T20:35:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-DocumentLOINCCodelist.xlsx
+++ b/ValueSet-DocumentLOINCCodelist.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-09T20:35:07+00:00</t>
+    <t>2025-04-09T22:25:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-DocumentLOINCCodelist.xlsx
+++ b/ValueSet-DocumentLOINCCodelist.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-09T22:25:52+00:00</t>
+    <t>2025-04-09T23:03:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
